--- a/artifacts/customer_benchmark_questions.xlsx
+++ b/artifacts/customer_benchmark_questions.xlsx
@@ -4638,7 +4638,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G118" t="b">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G119" t="b">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G121" t="b">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G122" t="b">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G123" t="b">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G124" t="b">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G125" t="b">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>refusal</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -7538,11 +7538,11 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -7778,11 +7778,11 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8018,11 +8018,11 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -8258,11 +8258,11 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -8498,11 +8498,11 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -8738,11 +8738,11 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9218,11 +9218,11 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -9458,11 +9458,11 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -9698,11 +9698,11 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -9938,11 +9938,11 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10178,11 +10178,11 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -10418,11 +10418,11 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -10658,11 +10658,11 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -10898,11 +10898,11 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="G281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
